--- a/Data/RossSea_Phenology_estimates2025.xlsx
+++ b/Data/RossSea_Phenology_estimates2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ucliveac-my.sharepoint.com/personal/rose_foster-dyer_canterbury_ac_nz/Documents/Github/SAR_RossSea_compare/SAR_RossSea_compare/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="418" documentId="8_{C36C3FC0-118D-426B-A4A0-6E6EFE06D4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66C67A82-EF55-4A6F-9D59-63D52FF5B665}"/>
+  <xr:revisionPtr revIDLastSave="538" documentId="8_{C36C3FC0-118D-426B-A4A0-6E6EFE06D4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24680445-3149-4073-8D2C-EC9960491987}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D741B97E-D510-4026-838A-5DA85EBB5CBC}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5247" uniqueCount="1639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5323" uniqueCount="1638">
   <si>
     <t>Beaufort</t>
   </si>
@@ -4955,9 +4955,6 @@
   </si>
   <si>
     <t>17:10:58 UTC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADD 2024 FRANKLIN SAR DATA AND BP ESTIMATES FROM BOTH YEARS </t>
   </si>
   <si>
     <t xml:space="preserve">ADD ROGET CHICKS, SAR ESTIMATES, AND BP ESTIMATES FROM BOTH YEARS </t>
@@ -13666,7 +13663,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B1A0D2B-4DC1-4917-B8F0-45E72FC1BE7E}">
-  <dimension ref="A1:AP98"/>
+  <dimension ref="A1:AP121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="16.85546875" customWidth="1"/>
@@ -13971,7 +13968,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="D10" s="1">
         <v>45933</v>
@@ -14587,7 +14584,7 @@
         <v>112</v>
       </c>
       <c r="C25" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="D25" s="1">
         <v>45929</v>
@@ -14610,10 +14607,12 @@
       <c r="J25">
         <v>-157.715</v>
       </c>
-      <c r="K25" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="L25" s="4"/>
+      <c r="K25" s="6">
+        <v>160987.53357217001</v>
+      </c>
+      <c r="L25" s="6">
+        <v>17148.025596260999</v>
+      </c>
       <c r="M25" t="s">
         <v>1072</v>
       </c>
@@ -14626,7 +14625,7 @@
         <v>112</v>
       </c>
       <c r="C26" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="D26" s="1">
         <v>45583</v>
@@ -17470,168 +17469,129 @@
     </row>
     <row r="86" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>451</v>
+        <v>364</v>
       </c>
       <c r="B86" t="s">
-        <v>452</v>
+        <v>365</v>
       </c>
       <c r="C86" t="s">
-        <v>1075</v>
-      </c>
-      <c r="D86" s="1">
-        <v>45771</v>
-      </c>
-      <c r="E86">
-        <v>4</v>
-      </c>
-      <c r="F86">
-        <v>24</v>
+        <v>1077</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="E86" s="16" t="s">
+        <v>885</v>
+      </c>
+      <c r="F86" t="s">
+        <v>885</v>
       </c>
       <c r="G86">
-        <v>2025</v>
-      </c>
-      <c r="H86">
-        <v>114</v>
+        <v>2024</v>
+      </c>
+      <c r="H86" t="s">
+        <v>885</v>
       </c>
       <c r="I86">
-        <v>-76.177379999999999</v>
+        <v>-77.459999999999994</v>
       </c>
       <c r="J86">
-        <v>168.394475</v>
+        <v>169.32</v>
       </c>
       <c r="K86" s="6">
-        <v>3965.1596362438199</v>
+        <v>1332.22398527275</v>
       </c>
       <c r="L86" s="6">
-        <v>457.06102312336998</v>
+        <v>232.35302783361001</v>
       </c>
       <c r="M86" t="s">
-        <v>890</v>
-      </c>
-      <c r="Y86" s="2"/>
-      <c r="Z86" s="3"/>
-      <c r="AB86" s="1"/>
-      <c r="AC86" s="2"/>
-      <c r="AD86" s="4"/>
-      <c r="AE86" s="4"/>
-      <c r="AF86" s="4"/>
-      <c r="AH86" s="4"/>
-      <c r="AJ86" s="4"/>
-      <c r="AK86" s="5"/>
-      <c r="AM86" s="4"/>
-      <c r="AN86" s="4"/>
-      <c r="AO86" s="4"/>
-      <c r="AP86" s="4"/>
+        <v>1076</v>
+      </c>
+      <c r="N86" t="s">
+        <v>1081</v>
+      </c>
     </row>
     <row r="87" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>451</v>
+        <v>364</v>
       </c>
       <c r="B87" t="s">
-        <v>452</v>
+        <v>365</v>
       </c>
       <c r="C87" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="D87" s="1">
-        <v>45799</v>
+        <v>45940</v>
       </c>
       <c r="E87">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F87">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G87">
         <v>2025</v>
       </c>
       <c r="H87">
-        <v>142</v>
+        <v>283</v>
       </c>
       <c r="I87">
-        <v>-76.177379999999999</v>
+        <v>-77.459999999999994</v>
       </c>
       <c r="J87">
-        <v>168.394475</v>
+        <v>169.32</v>
       </c>
       <c r="K87" s="6">
-        <v>7647.7212372112799</v>
+        <v>1715.3462213370599</v>
       </c>
       <c r="L87" s="6">
-        <v>876.19835676202104</v>
+        <v>330.47912272201398</v>
       </c>
       <c r="M87" t="s">
-        <v>890</v>
-      </c>
-      <c r="Y87" s="2"/>
-      <c r="Z87" s="3"/>
-      <c r="AB87" s="1"/>
-      <c r="AC87" s="2"/>
-      <c r="AD87" s="4"/>
-      <c r="AE87" s="4"/>
-      <c r="AF87" s="4"/>
-      <c r="AH87" s="4"/>
-      <c r="AJ87" s="4"/>
-      <c r="AK87" s="5"/>
-      <c r="AM87" s="4"/>
-      <c r="AN87" s="4"/>
-      <c r="AO87" s="4"/>
-      <c r="AP87" s="4"/>
+        <v>1076</v>
+      </c>
     </row>
     <row r="88" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>451</v>
+        <v>364</v>
       </c>
       <c r="B88" t="s">
-        <v>452</v>
+        <v>365</v>
       </c>
       <c r="C88" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="D88" s="1">
-        <v>45822</v>
+        <v>45940</v>
       </c>
       <c r="E88">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F88">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G88">
         <v>2025</v>
       </c>
       <c r="H88">
-        <v>165</v>
+        <v>283</v>
       </c>
       <c r="I88">
-        <v>-76.177379999999999</v>
+        <v>-77.459999999999994</v>
       </c>
       <c r="J88">
-        <v>168.394475</v>
+        <v>169.32</v>
       </c>
       <c r="K88" s="6">
-        <v>7328.1058100090204</v>
+        <v>15571.724936475901</v>
       </c>
       <c r="L88" s="6">
-        <v>830.05839044497202</v>
+        <v>1662.40745709719</v>
       </c>
       <c r="M88" t="s">
-        <v>890</v>
-      </c>
-      <c r="Y88" s="2"/>
-      <c r="Z88" s="3"/>
-      <c r="AB88" s="1"/>
-      <c r="AC88" s="2"/>
-      <c r="AD88" s="4"/>
-      <c r="AE88" s="4"/>
-      <c r="AF88" s="4"/>
-      <c r="AH88" s="4"/>
-      <c r="AI88" s="4"/>
-      <c r="AJ88" s="4"/>
-      <c r="AK88" s="5"/>
-      <c r="AN88" s="4"/>
-      <c r="AO88" s="4"/>
-      <c r="AP88" s="4"/>
+        <v>1072</v>
+      </c>
     </row>
     <row r="89" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
@@ -17644,19 +17604,19 @@
         <v>1075</v>
       </c>
       <c r="D89" s="1">
-        <v>45838</v>
+        <v>45771</v>
       </c>
       <c r="E89">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F89">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G89">
         <v>2025</v>
       </c>
       <c r="H89">
-        <v>181</v>
+        <v>114</v>
       </c>
       <c r="I89">
         <v>-76.177379999999999</v>
@@ -17665,10 +17625,10 @@
         <v>168.394475</v>
       </c>
       <c r="K89" s="6">
-        <v>3998.0101875238402</v>
+        <v>3965.1596362438199</v>
       </c>
       <c r="L89" s="6">
-        <v>471.17662845861599</v>
+        <v>457.06102312336998</v>
       </c>
       <c r="M89" t="s">
         <v>890</v>
@@ -17681,7 +17641,6 @@
       <c r="AE89" s="4"/>
       <c r="AF89" s="4"/>
       <c r="AH89" s="4"/>
-      <c r="AI89" s="4"/>
       <c r="AJ89" s="4"/>
       <c r="AK89" s="5"/>
       <c r="AM89" s="4"/>
@@ -17700,10 +17659,10 @@
         <v>1075</v>
       </c>
       <c r="D90" s="1">
-        <v>45860</v>
+        <v>45799</v>
       </c>
       <c r="E90">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F90">
         <v>22</v>
@@ -17712,7 +17671,7 @@
         <v>2025</v>
       </c>
       <c r="H90">
-        <v>203</v>
+        <v>142</v>
       </c>
       <c r="I90">
         <v>-76.177379999999999</v>
@@ -17721,10 +17680,10 @@
         <v>168.394475</v>
       </c>
       <c r="K90" s="6">
-        <v>4593.9585123347897</v>
+        <v>7647.7212372112799</v>
       </c>
       <c r="L90" s="6">
-        <v>550.01906649850605</v>
+        <v>876.19835676202104</v>
       </c>
       <c r="M90" t="s">
         <v>890</v>
@@ -17737,7 +17696,6 @@
       <c r="AE90" s="4"/>
       <c r="AF90" s="4"/>
       <c r="AH90" s="4"/>
-      <c r="AI90" s="4"/>
       <c r="AJ90" s="4"/>
       <c r="AK90" s="5"/>
       <c r="AM90" s="4"/>
@@ -17756,19 +17714,19 @@
         <v>1075</v>
       </c>
       <c r="D91" s="1">
-        <v>45875</v>
+        <v>45822</v>
       </c>
       <c r="E91">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F91">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G91">
         <v>2025</v>
       </c>
       <c r="H91">
-        <v>218</v>
+        <v>165</v>
       </c>
       <c r="I91">
         <v>-76.177379999999999</v>
@@ -17777,10 +17735,10 @@
         <v>168.394475</v>
       </c>
       <c r="K91" s="6">
-        <v>4363.3147492279704</v>
+        <v>7328.1058100090204</v>
       </c>
       <c r="L91" s="6">
-        <v>507.39987446001999</v>
+        <v>830.05839044497202</v>
       </c>
       <c r="M91" t="s">
         <v>890</v>
@@ -17796,8 +17754,8 @@
       <c r="AI91" s="4"/>
       <c r="AJ91" s="4"/>
       <c r="AK91" s="5"/>
-      <c r="AM91" s="4"/>
       <c r="AN91" s="4"/>
+      <c r="AO91" s="4"/>
       <c r="AP91" s="4"/>
     </row>
     <row r="92" spans="1:42" x14ac:dyDescent="0.25">
@@ -17811,19 +17769,19 @@
         <v>1075</v>
       </c>
       <c r="D92" s="1">
-        <v>45893</v>
+        <v>45838</v>
       </c>
       <c r="E92">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F92">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G92">
         <v>2025</v>
       </c>
       <c r="H92">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="I92">
         <v>-76.177379999999999</v>
@@ -17832,10 +17790,10 @@
         <v>168.394475</v>
       </c>
       <c r="K92" s="6">
-        <v>7130.7910803292198</v>
+        <v>3998.0101875238402</v>
       </c>
       <c r="L92" s="6">
-        <v>655.53063714181701</v>
+        <v>471.17662845861599</v>
       </c>
       <c r="M92" t="s">
         <v>890</v>
@@ -17848,6 +17806,7 @@
       <c r="AE92" s="4"/>
       <c r="AF92" s="4"/>
       <c r="AH92" s="4"/>
+      <c r="AI92" s="4"/>
       <c r="AJ92" s="4"/>
       <c r="AK92" s="5"/>
       <c r="AM92" s="4"/>
@@ -17857,17 +17816,780 @@
     </row>
     <row r="93" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1636</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="B93" t="s">
+        <v>452</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D93" s="1">
+        <v>45860</v>
+      </c>
+      <c r="E93">
+        <v>7</v>
+      </c>
+      <c r="F93">
+        <v>22</v>
+      </c>
+      <c r="G93">
+        <v>2025</v>
+      </c>
+      <c r="H93">
+        <v>203</v>
+      </c>
+      <c r="I93">
+        <v>-76.177379999999999</v>
+      </c>
+      <c r="J93">
+        <v>168.394475</v>
+      </c>
+      <c r="K93" s="6">
+        <v>4593.9585123347897</v>
+      </c>
+      <c r="L93" s="6">
+        <v>550.01906649850605</v>
+      </c>
+      <c r="M93" t="s">
+        <v>890</v>
+      </c>
+      <c r="Y93" s="2"/>
+      <c r="Z93" s="3"/>
+      <c r="AB93" s="1"/>
+      <c r="AC93" s="2"/>
+      <c r="AD93" s="4"/>
+      <c r="AE93" s="4"/>
+      <c r="AF93" s="4"/>
+      <c r="AH93" s="4"/>
+      <c r="AI93" s="4"/>
+      <c r="AJ93" s="4"/>
+      <c r="AK93" s="5"/>
+      <c r="AM93" s="4"/>
+      <c r="AN93" s="4"/>
+      <c r="AO93" s="4"/>
+      <c r="AP93" s="4"/>
+    </row>
+    <row r="94" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>451</v>
+      </c>
+      <c r="B94" t="s">
+        <v>452</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D94" s="1">
+        <v>45875</v>
+      </c>
+      <c r="E94">
+        <v>8</v>
+      </c>
+      <c r="F94">
+        <v>6</v>
+      </c>
+      <c r="G94">
+        <v>2025</v>
+      </c>
+      <c r="H94">
+        <v>218</v>
+      </c>
+      <c r="I94">
+        <v>-76.177379999999999</v>
+      </c>
+      <c r="J94">
+        <v>168.394475</v>
+      </c>
+      <c r="K94" s="6">
+        <v>4363.3147492279704</v>
+      </c>
+      <c r="L94" s="6">
+        <v>507.39987446001999</v>
+      </c>
+      <c r="M94" t="s">
+        <v>890</v>
+      </c>
+      <c r="Y94" s="2"/>
+      <c r="Z94" s="3"/>
+      <c r="AB94" s="1"/>
+      <c r="AC94" s="2"/>
+      <c r="AD94" s="4"/>
+      <c r="AE94" s="4"/>
+      <c r="AF94" s="4"/>
+      <c r="AH94" s="4"/>
+      <c r="AI94" s="4"/>
+      <c r="AJ94" s="4"/>
+      <c r="AK94" s="5"/>
+      <c r="AM94" s="4"/>
+      <c r="AN94" s="4"/>
+      <c r="AP94" s="4"/>
+    </row>
+    <row r="95" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>451</v>
+      </c>
+      <c r="B95" t="s">
+        <v>452</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D95" s="1">
+        <v>45893</v>
+      </c>
+      <c r="E95">
+        <v>8</v>
+      </c>
+      <c r="F95">
+        <v>24</v>
+      </c>
+      <c r="G95">
+        <v>2025</v>
+      </c>
+      <c r="H95">
+        <v>236</v>
+      </c>
+      <c r="I95">
+        <v>-76.177379999999999</v>
+      </c>
+      <c r="J95">
+        <v>168.394475</v>
+      </c>
+      <c r="K95" s="6">
+        <v>7130.7910803292198</v>
+      </c>
+      <c r="L95" s="6">
+        <v>655.53063714181701</v>
+      </c>
+      <c r="M95" t="s">
+        <v>890</v>
+      </c>
+      <c r="Y95" s="2"/>
+      <c r="Z95" s="3"/>
+      <c r="AB95" s="1"/>
+      <c r="AC95" s="2"/>
+      <c r="AD95" s="4"/>
+      <c r="AE95" s="4"/>
+      <c r="AF95" s="4"/>
+      <c r="AH95" s="4"/>
+      <c r="AJ95" s="4"/>
+      <c r="AK95" s="5"/>
+      <c r="AM95" s="4"/>
+      <c r="AN95" s="4"/>
+      <c r="AO95" s="4"/>
+      <c r="AP95" s="4"/>
     </row>
     <row r="96" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>451</v>
+      </c>
+      <c r="B96" t="s">
+        <v>452</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D96" s="1">
+        <v>45405</v>
+      </c>
+      <c r="E96">
+        <v>4</v>
+      </c>
+      <c r="F96">
+        <v>23</v>
+      </c>
+      <c r="G96">
+        <v>2024</v>
+      </c>
+      <c r="H96">
+        <v>114</v>
+      </c>
+      <c r="I96">
+        <v>-76.177109340000001</v>
+      </c>
+      <c r="J96">
+        <v>168.3951361</v>
+      </c>
+      <c r="K96" s="6">
+        <v>749.76901485221595</v>
+      </c>
+      <c r="L96" s="6">
+        <v>87.714691351420996</v>
+      </c>
+      <c r="M96" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>451</v>
+      </c>
+      <c r="B97" t="s">
+        <v>452</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D97" s="1">
+        <v>45411</v>
+      </c>
+      <c r="E97">
+        <v>4</v>
+      </c>
+      <c r="F97">
+        <v>29</v>
+      </c>
+      <c r="G97">
+        <v>2024</v>
+      </c>
+      <c r="H97">
+        <v>120</v>
+      </c>
+      <c r="I97">
+        <v>-76.177269089999996</v>
+      </c>
+      <c r="J97">
+        <v>168.3912272</v>
+      </c>
+      <c r="K97" s="6">
+        <v>5890.3041012563999</v>
+      </c>
+      <c r="L97" s="6">
+        <v>658.60133209721403</v>
+      </c>
+      <c r="M97" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>451</v>
+      </c>
+      <c r="B98" t="s">
+        <v>452</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D98" s="1">
+        <v>45414</v>
+      </c>
+      <c r="E98">
+        <v>5</v>
+      </c>
+      <c r="F98">
+        <v>2</v>
+      </c>
+      <c r="G98">
+        <v>2024</v>
+      </c>
+      <c r="H98">
+        <v>123</v>
+      </c>
+      <c r="I98">
+        <v>-76.177269089999996</v>
+      </c>
+      <c r="J98">
+        <v>168.3912272</v>
+      </c>
+      <c r="K98" s="6">
+        <v>14988.7591448315</v>
+      </c>
+      <c r="L98" s="6">
+        <v>1770.3214415316399</v>
+      </c>
+      <c r="M98" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>451</v>
+      </c>
+      <c r="B99" t="s">
+        <v>452</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D99" s="1">
+        <v>45421</v>
+      </c>
+      <c r="E99">
+        <v>5</v>
+      </c>
+      <c r="F99">
+        <v>9</v>
+      </c>
+      <c r="G99">
+        <v>2024</v>
+      </c>
+      <c r="H99">
+        <v>130</v>
+      </c>
+      <c r="I99">
+        <v>-76.177339900000007</v>
+      </c>
+      <c r="J99">
+        <v>168.39055283636301</v>
+      </c>
+      <c r="K99" s="6">
+        <v>7635.8438715213997</v>
+      </c>
+      <c r="L99" s="6">
+        <v>899.52158255817005</v>
+      </c>
+      <c r="M99" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>451</v>
+      </c>
+      <c r="B100" t="s">
+        <v>452</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D100" s="1">
+        <v>45429</v>
+      </c>
+      <c r="E100">
+        <v>5</v>
+      </c>
+      <c r="F100">
+        <v>17</v>
+      </c>
+      <c r="G100">
+        <v>2024</v>
+      </c>
+      <c r="H100">
+        <v>138</v>
+      </c>
+      <c r="I100">
+        <v>-76.177269089999996</v>
+      </c>
+      <c r="J100">
+        <v>168.3912272</v>
+      </c>
+      <c r="K100" s="6">
+        <v>6808.6982037543203</v>
+      </c>
+      <c r="L100" s="6">
+        <v>778.04766848198506</v>
+      </c>
+      <c r="M100" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>451</v>
+      </c>
+      <c r="B101" t="s">
+        <v>452</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D101" s="1">
+        <v>45436</v>
+      </c>
+      <c r="E101">
+        <v>5</v>
+      </c>
+      <c r="F101">
+        <v>24</v>
+      </c>
+      <c r="G101">
+        <v>2024</v>
+      </c>
+      <c r="H101">
+        <v>145</v>
+      </c>
+      <c r="I101">
+        <v>-76.177901989999995</v>
+      </c>
+      <c r="J101">
+        <v>168.39030080000001</v>
+      </c>
+      <c r="K101" s="6">
+        <v>8641.2272690371192</v>
+      </c>
+      <c r="L101" s="6">
+        <v>981.73728850358805</v>
+      </c>
+      <c r="M101" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>451</v>
+      </c>
+      <c r="B102" t="s">
+        <v>452</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D102" s="1">
+        <v>45450</v>
+      </c>
+      <c r="E102">
+        <v>6</v>
+      </c>
+      <c r="F102">
+        <v>7</v>
+      </c>
+      <c r="G102">
+        <v>2024</v>
+      </c>
+      <c r="H102">
+        <v>159</v>
+      </c>
+      <c r="I102">
+        <v>-76.177457070000003</v>
+      </c>
+      <c r="J102">
+        <v>168.3915643</v>
+      </c>
+      <c r="K102" s="6">
+        <v>6247.1081380949099</v>
+      </c>
+      <c r="L102" s="6">
+        <v>736.35055743390103</v>
+      </c>
+      <c r="M102" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>451</v>
+      </c>
+      <c r="B103" t="s">
+        <v>452</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D103" s="1">
+        <v>45467</v>
+      </c>
+      <c r="E103">
+        <v>6</v>
+      </c>
+      <c r="F103">
+        <v>24</v>
+      </c>
+      <c r="G103">
+        <v>2024</v>
+      </c>
+      <c r="H103">
+        <v>176</v>
+      </c>
+      <c r="I103">
+        <v>-76.177269089999996</v>
+      </c>
+      <c r="J103">
+        <v>168.3912272</v>
+      </c>
+      <c r="K103" s="6">
+        <v>5029.9291930947802</v>
+      </c>
+      <c r="L103" s="6">
+        <v>581.62305574287996</v>
+      </c>
+      <c r="M103" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>451</v>
+      </c>
+      <c r="B104" t="s">
+        <v>452</v>
+      </c>
+      <c r="C104" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D104" s="1">
+        <v>45513</v>
+      </c>
+      <c r="E104">
+        <v>8</v>
+      </c>
+      <c r="F104">
+        <v>9</v>
+      </c>
+      <c r="G104">
+        <v>2024</v>
+      </c>
+      <c r="H104">
+        <v>222</v>
+      </c>
+      <c r="I104">
+        <v>-76.176363300000006</v>
+      </c>
+      <c r="J104">
+        <v>168.39021854285701</v>
+      </c>
+      <c r="K104" s="6">
+        <v>5089.5631022252101</v>
+      </c>
+      <c r="L104" s="6">
+        <v>564.05032868390799</v>
+      </c>
+      <c r="M104" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>451</v>
+      </c>
+      <c r="B105" t="s">
+        <v>452</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D105" s="1">
+        <v>45492</v>
+      </c>
+      <c r="E105">
+        <v>7</v>
+      </c>
+      <c r="F105">
+        <v>19</v>
+      </c>
+      <c r="G105">
+        <v>2025</v>
+      </c>
+      <c r="H105">
+        <v>200.67</v>
+      </c>
+      <c r="I105">
+        <v>-76.176363300000006</v>
+      </c>
+      <c r="J105">
+        <v>168.39021854285701</v>
+      </c>
+      <c r="K105" s="6">
+        <v>4318.43</v>
+      </c>
+      <c r="L105" s="6">
+        <v>538.26</v>
+      </c>
+      <c r="M105" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>451</v>
+      </c>
+      <c r="B106" t="s">
+        <v>452</v>
+      </c>
+      <c r="C106" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D106" s="1">
+        <v>45467</v>
+      </c>
+      <c r="E106">
+        <v>8</v>
+      </c>
+      <c r="F106">
+        <v>9</v>
+      </c>
+      <c r="G106">
+        <v>2024</v>
+      </c>
+      <c r="H106">
+        <v>176</v>
+      </c>
+      <c r="I106">
+        <v>-76.176363300000006</v>
+      </c>
+      <c r="J106">
+        <v>168.39021854285701</v>
+      </c>
+      <c r="K106" s="6">
+        <v>5029.93</v>
+      </c>
+      <c r="L106" s="6">
+        <v>581.62</v>
+      </c>
+      <c r="M106" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>451</v>
+      </c>
+      <c r="B107" t="s">
+        <v>452</v>
+      </c>
+      <c r="C107" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D107" t="s">
+        <v>885</v>
+      </c>
+      <c r="E107" t="s">
+        <v>885</v>
+      </c>
+      <c r="F107" t="s">
+        <v>885</v>
+      </c>
+      <c r="G107">
+        <v>2024</v>
+      </c>
+      <c r="H107" t="s">
+        <v>885</v>
+      </c>
+      <c r="I107">
+        <v>-76.180000000000007</v>
+      </c>
+      <c r="J107">
+        <v>168.43</v>
+      </c>
+      <c r="K107" s="6">
+        <v>3172.5315182796198</v>
+      </c>
+      <c r="L107" s="6">
+        <v>836.95163966881898</v>
+      </c>
+      <c r="M107" t="s">
+        <v>1076</v>
+      </c>
+      <c r="N107" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>451</v>
+      </c>
+      <c r="B108" t="s">
+        <v>452</v>
+      </c>
+      <c r="C108" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D108" s="1">
+        <v>45954</v>
+      </c>
+      <c r="E108">
+        <v>10</v>
+      </c>
+      <c r="F108">
+        <v>24</v>
+      </c>
+      <c r="G108">
+        <v>2025</v>
+      </c>
+      <c r="H108">
+        <v>297</v>
+      </c>
+      <c r="I108">
+        <v>-76.180000000000007</v>
+      </c>
+      <c r="J108">
+        <v>168.43</v>
+      </c>
+      <c r="K108" s="6">
+        <v>2998.2686839243902</v>
+      </c>
+      <c r="L108" s="6">
+        <v>847.33834295368604</v>
+      </c>
+      <c r="M108" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>451</v>
+      </c>
+      <c r="B109" t="s">
+        <v>452</v>
+      </c>
+      <c r="C109" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D109" s="1">
+        <v>45954</v>
+      </c>
+      <c r="E109">
+        <v>10</v>
+      </c>
+      <c r="F109">
+        <v>24</v>
+      </c>
+      <c r="G109">
+        <v>2025</v>
+      </c>
+      <c r="H109">
+        <v>297</v>
+      </c>
+      <c r="I109">
+        <v>-76.180000000000007</v>
+      </c>
+      <c r="J109">
+        <v>168.43</v>
+      </c>
+      <c r="K109" s="6">
+        <v>14857.1292518354</v>
+      </c>
+      <c r="L109" s="6">
+        <v>1432.4796890744101</v>
+      </c>
+      <c r="M109" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="E112" s="1"/>
+      <c r="F112" s="3"/>
+      <c r="K112" s="2"/>
+      <c r="L112" s="1"/>
+      <c r="N112" s="2"/>
+    </row>
+    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="Q113" s="4"/>
+    </row>
+    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D115" s="1"/>
+      <c r="E115" s="1"/>
+      <c r="T115" s="6"/>
+    </row>
+    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="G116" s="3"/>
+      <c r="M116" s="2"/>
+      <c r="N116" s="1"/>
+      <c r="P116" s="2"/>
+    </row>
+    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D118" s="1"/>
+      <c r="E118" s="1"/>
+    </row>
+    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A120" s="7" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A121" s="7" t="s">
         <v>1637</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>1638</v>
       </c>
     </row>
   </sheetData>
@@ -62865,8 +63587,9 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.7109375" style="6" customWidth="1"/>
-    <col min="20" max="20" width="9.140625" style="6"/>
+    <col min="20" max="20" width="16.85546875" style="6" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -63005,10 +63728,10 @@
         <v>-157.58000000000001</v>
       </c>
       <c r="D3" s="1">
+        <v>45846</v>
+      </c>
+      <c r="E3" s="1">
         <v>45889</v>
-      </c>
-      <c r="E3" s="1">
-        <v>45846</v>
       </c>
       <c r="F3">
         <v>205.2</v>
@@ -63413,7 +64136,7 @@
         <v>169.64</v>
       </c>
       <c r="D9" s="1">
-        <v>45468</v>
+        <v>45483</v>
       </c>
       <c r="E9" s="1">
         <v>45510</v>
@@ -63434,13 +64157,13 @@
         <v>16344.83</v>
       </c>
       <c r="K9">
+        <v>14561.66</v>
+      </c>
+      <c r="L9">
         <v>18146.310000000001</v>
       </c>
-      <c r="L9">
-        <v>14561.66</v>
-      </c>
       <c r="M9">
-        <v>-1792.33</v>
+        <v>1792.33</v>
       </c>
       <c r="N9">
         <v>3164.25</v>
@@ -63467,6 +64190,7 @@
         <v>29.2</v>
       </c>
       <c r="V9">
+        <f>I9*2</f>
         <v>32752.38</v>
       </c>
     </row>
@@ -63481,13 +64205,13 @@
         <v>169.28</v>
       </c>
       <c r="D10" s="1">
-        <v>45450</v>
+        <v>45467</v>
       </c>
       <c r="E10" s="1">
         <v>45489</v>
       </c>
       <c r="F10">
-        <v>182.67</v>
+        <v>188.33</v>
       </c>
       <c r="G10">
         <v>3</v>
@@ -63496,46 +64220,47 @@
         <v>909</v>
       </c>
       <c r="I10" s="6">
-        <v>2349.79</v>
+        <v>1825</v>
       </c>
       <c r="J10">
-        <v>1959.24</v>
+        <v>1796.07</v>
       </c>
       <c r="K10">
-        <v>2603.5</v>
+        <v>1618.23</v>
       </c>
       <c r="L10">
-        <v>2094.52</v>
+        <v>2027.91</v>
       </c>
       <c r="M10">
-        <v>-254.49</v>
+        <v>204.84</v>
       </c>
       <c r="N10">
-        <v>821.82</v>
+        <v>122.37</v>
       </c>
       <c r="O10">
-        <v>474.48</v>
+        <v>70.650000000000006</v>
       </c>
       <c r="P10">
-        <v>1875.31</v>
+        <v>1754.35</v>
       </c>
       <c r="Q10">
-        <v>2824.27</v>
+        <v>1895.65</v>
       </c>
       <c r="R10">
-        <v>1811.37</v>
+        <v>1608.32</v>
       </c>
       <c r="S10">
-        <v>2888.21</v>
+        <v>2041.68</v>
       </c>
       <c r="T10" s="6">
-        <v>538.41999999999996</v>
+        <v>216.68</v>
       </c>
       <c r="U10">
-        <v>45.8</v>
+        <v>23.7</v>
       </c>
       <c r="V10">
-        <v>4699.58</v>
+        <f t="shared" ref="V10:V13" si="0">I10*2</f>
+        <v>3650</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -63549,13 +64274,13 @@
         <v>168.39</v>
       </c>
       <c r="D11" s="1">
-        <v>45429</v>
+        <v>45467</v>
       </c>
       <c r="E11" s="1">
-        <v>45429</v>
+        <v>45467</v>
       </c>
       <c r="F11">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -63564,34 +64289,35 @@
         <v>908</v>
       </c>
       <c r="I11" s="6">
-        <v>6808.7</v>
+        <v>5029.93</v>
       </c>
       <c r="J11">
-        <v>6808.7</v>
+        <v>5029.93</v>
       </c>
       <c r="K11">
-        <v>7579.88</v>
+        <v>4436.88</v>
       </c>
       <c r="L11">
-        <v>6023.78</v>
+        <v>5600.13</v>
       </c>
       <c r="M11">
-        <v>-778.05</v>
+        <v>581.62</v>
       </c>
       <c r="R11">
-        <v>7586.75</v>
+        <v>4448.3100000000004</v>
       </c>
       <c r="S11">
-        <v>6030.65</v>
+        <v>5611.55</v>
       </c>
       <c r="T11" s="6">
-        <v>-778.05</v>
+        <v>581.62</v>
       </c>
       <c r="U11">
-        <v>-22.9</v>
+        <v>23.1</v>
       </c>
       <c r="V11">
-        <v>13617.4</v>
+        <f t="shared" si="0"/>
+        <v>10059.86</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
@@ -63626,13 +64352,13 @@
         <v>4990.1499999999996</v>
       </c>
       <c r="K12">
+        <v>4715.57</v>
+      </c>
+      <c r="L12">
         <v>5806.73</v>
       </c>
-      <c r="L12">
-        <v>4715.57</v>
-      </c>
       <c r="M12">
-        <v>-545.58000000000004</v>
+        <v>545.58000000000004</v>
       </c>
       <c r="N12">
         <v>1527.47</v>
@@ -63659,6 +64385,7 @@
         <v>35.700000000000003</v>
       </c>
       <c r="V12">
+        <f t="shared" si="0"/>
         <v>10522.9</v>
       </c>
     </row>
@@ -63694,13 +64421,13 @@
         <v>10307.290000000001</v>
       </c>
       <c r="K13">
+        <v>9264.18</v>
+      </c>
+      <c r="L13">
         <v>11396.65</v>
       </c>
-      <c r="L13">
-        <v>9264.18</v>
-      </c>
       <c r="M13">
-        <v>-1066.24</v>
+        <v>1066.24</v>
       </c>
       <c r="N13">
         <v>3138.83</v>
@@ -63727,6 +64454,7 @@
         <v>36.700000000000003</v>
       </c>
       <c r="V13">
+        <f t="shared" si="0"/>
         <v>20682.48</v>
       </c>
     </row>

--- a/Data/RossSea_Phenology_estimates2025.xlsx
+++ b/Data/RossSea_Phenology_estimates2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ucliveac-my.sharepoint.com/personal/rose_foster-dyer_canterbury_ac_nz/Documents/Github/SAR_RossSea_compare/SAR_RossSea_compare/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="738" documentId="8_{C36C3FC0-118D-426B-A4A0-6E6EFE06D4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E7C297B-C273-42C7-BE10-EA410BDF0739}"/>
+  <xr:revisionPtr revIDLastSave="743" documentId="8_{C36C3FC0-118D-426B-A4A0-6E6EFE06D4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FB9C0A5-47E6-4804-BDE6-B5F112F8FEFB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D741B97E-D510-4026-838A-5DA85EBB5CBC}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D741B97E-D510-4026-838A-5DA85EBB5CBC}"/>
   </bookViews>
   <sheets>
     <sheet name="full combined" sheetId="9" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3719" uniqueCount="1085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3724" uniqueCount="1085">
   <si>
     <t>Beaufort</t>
   </si>
@@ -3393,10 +3393,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3716,7 +3712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B1A0D2B-4DC1-4917-B8F0-45E72FC1BE7E}">
-  <dimension ref="A1:AU165"/>
+  <dimension ref="A1:AU166"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" customWidth="1"/>
@@ -7292,14 +7288,13 @@
       <c r="J75">
         <v>168.394475</v>
       </c>
-      <c r="K75" s="6">
-        <v>7130.7910803292198</v>
-      </c>
-      <c r="L75" s="6">
-        <v>655.53063714181701</v>
-      </c>
+      <c r="K75" s="6"/>
+      <c r="L75" s="6"/>
       <c r="M75" t="s">
         <v>890</v>
+      </c>
+      <c r="N75" t="s">
+        <v>1081</v>
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" s="3"/>
@@ -10571,7 +10566,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="152" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>240</v>
       </c>
@@ -10617,81 +10612,81 @@
     </row>
     <row r="153" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>364</v>
+        <v>240</v>
       </c>
       <c r="B153" t="s">
-        <v>365</v>
+        <v>241</v>
       </c>
       <c r="C153" t="s">
         <v>1076</v>
       </c>
       <c r="D153" s="1">
-        <v>45940</v>
+        <v>45577</v>
       </c>
       <c r="E153">
         <v>10</v>
       </c>
       <c r="F153">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G153">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H153">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I153">
-        <v>-77.459999999999994</v>
+        <v>-73.348299999999995</v>
       </c>
       <c r="J153">
-        <v>169.32</v>
+        <v>169.6242</v>
       </c>
       <c r="K153" s="6">
-        <v>15571.724936475901</v>
+        <v>12045.8161844612</v>
       </c>
       <c r="L153" s="6">
-        <v>1662.40745709719</v>
+        <v>2349.1057802120499</v>
       </c>
       <c r="M153" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="154" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>451</v>
+        <v>364</v>
       </c>
       <c r="B154" t="s">
-        <v>452</v>
+        <v>365</v>
       </c>
       <c r="C154" t="s">
         <v>1076</v>
       </c>
       <c r="D154" s="1">
-        <v>45954</v>
+        <v>45940</v>
       </c>
       <c r="E154">
         <v>10</v>
       </c>
       <c r="F154">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G154">
         <v>2025</v>
       </c>
       <c r="H154">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="I154">
-        <v>-76.180000000000007</v>
+        <v>-77.459999999999994</v>
       </c>
       <c r="J154">
-        <v>168.43</v>
+        <v>169.32</v>
       </c>
       <c r="K154" s="6">
-        <v>14857.1292518354</v>
+        <v>15571.724936475901</v>
       </c>
       <c r="L154" s="6">
-        <v>1432.4796890744101</v>
+        <v>1662.40745709719</v>
       </c>
       <c r="M154" t="s">
         <v>1071</v>
@@ -10699,48 +10694,44 @@
     </row>
     <row r="155" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>538</v>
+        <v>451</v>
       </c>
       <c r="B155" t="s">
-        <v>539</v>
+        <v>452</v>
       </c>
       <c r="C155" t="s">
         <v>1076</v>
       </c>
       <c r="D155" s="1">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="E155">
         <v>10</v>
       </c>
       <c r="F155">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G155">
         <v>2025</v>
       </c>
       <c r="H155">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I155">
-        <v>-71.989999999999995</v>
+        <v>-76.180000000000007</v>
       </c>
       <c r="J155">
-        <v>170.59</v>
+        <v>168.43</v>
       </c>
       <c r="K155" s="6">
-        <v>21047.738580909601</v>
+        <v>14857.1292518354</v>
       </c>
       <c r="L155" s="6">
-        <v>1843.9509106179</v>
+        <v>1432.4796890744101</v>
       </c>
       <c r="M155" t="s">
         <v>1071</v>
       </c>
-      <c r="P155" s="1"/>
-      <c r="R155" s="2"/>
-      <c r="AA155" s="6"/>
-      <c r="AH155" s="6"/>
     </row>
     <row r="156" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
@@ -10753,19 +10744,19 @@
         <v>1076</v>
       </c>
       <c r="D156" s="1">
-        <v>45576</v>
+        <v>45952</v>
       </c>
       <c r="E156">
         <v>10</v>
       </c>
       <c r="F156">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G156">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H156">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="I156">
         <v>-71.989999999999995</v>
@@ -10774,57 +10765,61 @@
         <v>170.59</v>
       </c>
       <c r="K156" s="6">
-        <v>27025.461131918699</v>
+        <v>21047.738580909601</v>
       </c>
       <c r="L156" s="6">
-        <v>2291.10923126333</v>
+        <v>1843.9509106179</v>
       </c>
       <c r="M156" t="s">
         <v>1071</v>
       </c>
-      <c r="N156" s="1"/>
-      <c r="P156" s="2"/>
+      <c r="P156" s="1"/>
+      <c r="R156" s="2"/>
+      <c r="AA156" s="6"/>
+      <c r="AH156" s="6"/>
     </row>
     <row r="157" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>623</v>
+        <v>538</v>
       </c>
       <c r="B157" t="s">
-        <v>624</v>
+        <v>539</v>
       </c>
       <c r="C157" t="s">
         <v>1076</v>
       </c>
       <c r="D157" s="1">
-        <v>45592</v>
+        <v>45576</v>
       </c>
       <c r="E157">
         <v>10</v>
       </c>
       <c r="F157">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G157">
         <v>2024</v>
       </c>
       <c r="H157">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="I157">
-        <v>-74.64</v>
+        <v>-71.989999999999995</v>
       </c>
       <c r="J157">
-        <v>165.37</v>
+        <v>170.59</v>
       </c>
       <c r="K157" s="6">
-        <v>46595.072714885602</v>
+        <v>27025.461131918699</v>
       </c>
       <c r="L157" s="6">
-        <v>3317.9884023903001</v>
+        <v>2291.10923126333</v>
       </c>
       <c r="M157" t="s">
         <v>1071</v>
       </c>
+      <c r="N157" s="1"/>
+      <c r="P157" s="2"/>
     </row>
     <row r="158" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
@@ -10837,19 +10832,19 @@
         <v>1076</v>
       </c>
       <c r="D158" s="1">
-        <v>45962</v>
+        <v>45592</v>
       </c>
       <c r="E158">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F158">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G158">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H158">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I158">
         <v>-74.64</v>
@@ -10858,21 +10853,55 @@
         <v>165.37</v>
       </c>
       <c r="K158" s="6">
-        <v>31907.045011811399</v>
+        <v>46595.072714885602</v>
       </c>
       <c r="L158" s="6">
-        <v>2685.7328438259501</v>
+        <v>3317.9884023903001</v>
       </c>
       <c r="M158" t="s">
         <v>1071</v>
       </c>
     </row>
-    <row r="160" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="E160" s="1"/>
-      <c r="F160" s="3"/>
-      <c r="K160" s="2"/>
-      <c r="L160" s="1"/>
-      <c r="N160" s="2"/>
+    <row r="159" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>623</v>
+      </c>
+      <c r="B159" t="s">
+        <v>624</v>
+      </c>
+      <c r="C159" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D159" s="1">
+        <v>45962</v>
+      </c>
+      <c r="E159">
+        <v>11</v>
+      </c>
+      <c r="F159">
+        <v>1</v>
+      </c>
+      <c r="G159">
+        <v>2025</v>
+      </c>
+      <c r="H159">
+        <v>305</v>
+      </c>
+      <c r="I159">
+        <v>-74.64</v>
+      </c>
+      <c r="J159">
+        <v>165.37</v>
+      </c>
+      <c r="K159" s="6">
+        <v>31907.045011811399</v>
+      </c>
+      <c r="L159" s="6">
+        <v>2685.7328438259501</v>
+      </c>
+      <c r="M159" t="s">
+        <v>1071</v>
+      </c>
     </row>
     <row r="161" spans="5:16" x14ac:dyDescent="0.25">
       <c r="E161" s="1"/>
@@ -10881,17 +10910,24 @@
       <c r="L161" s="1"/>
       <c r="N161" s="2"/>
     </row>
-    <row r="164" spans="5:16" x14ac:dyDescent="0.25">
-      <c r="G164" s="3"/>
-      <c r="M164" s="2"/>
-      <c r="N164" s="1"/>
-      <c r="P164" s="2"/>
+    <row r="162" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="E162" s="1"/>
+      <c r="F162" s="3"/>
+      <c r="K162" s="2"/>
+      <c r="L162" s="1"/>
+      <c r="N162" s="2"/>
     </row>
     <row r="165" spans="5:16" x14ac:dyDescent="0.25">
       <c r="G165" s="3"/>
       <c r="M165" s="2"/>
       <c r="N165" s="1"/>
       <c r="P165" s="2"/>
+    </row>
+    <row r="166" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="G166" s="3"/>
+      <c r="M166" s="2"/>
+      <c r="N166" s="1"/>
+      <c r="P166" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AU1" xr:uid="{7B1A0D2B-4DC1-4917-B8F0-45E72FC1BE7E}">
@@ -32205,6 +32241,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Data/RossSea_Phenology_estimates2025.xlsx
+++ b/Data/RossSea_Phenology_estimates2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ucliveac-my.sharepoint.com/personal/rose_foster-dyer_canterbury_ac_nz/Documents/Github/SAR_RossSea_compare/SAR_RossSea_compare/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="743" documentId="8_{C36C3FC0-118D-426B-A4A0-6E6EFE06D4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FB9C0A5-47E6-4804-BDE6-B5F112F8FEFB}"/>
+  <xr:revisionPtr revIDLastSave="744" documentId="8_{C36C3FC0-118D-426B-A4A0-6E6EFE06D4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C40784D-A320-4B13-AD42-EF5F0C38E411}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D741B97E-D510-4026-838A-5DA85EBB5CBC}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{D741B97E-D510-4026-838A-5DA85EBB5CBC}"/>
   </bookViews>
   <sheets>
     <sheet name="full combined" sheetId="9" r:id="rId1"/>
@@ -29640,6 +29640,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="10" max="10" width="25.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">

--- a/Data/RossSea_Phenology_estimates2025.xlsx
+++ b/Data/RossSea_Phenology_estimates2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ucliveac-my.sharepoint.com/personal/rose_foster-dyer_canterbury_ac_nz/Documents/Github/SAR_RossSea_compare/SAR_RossSea_compare/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="744" documentId="8_{C36C3FC0-118D-426B-A4A0-6E6EFE06D4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C40784D-A320-4B13-AD42-EF5F0C38E411}"/>
+  <xr:revisionPtr revIDLastSave="746" documentId="8_{C36C3FC0-118D-426B-A4A0-6E6EFE06D4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2842CF00-ADF4-418C-B4AB-77FEC13AA405}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{D741B97E-D510-4026-838A-5DA85EBB5CBC}"/>
+    <workbookView xWindow="28680" yWindow="555" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D741B97E-D510-4026-838A-5DA85EBB5CBC}"/>
   </bookViews>
   <sheets>
     <sheet name="full combined" sheetId="9" r:id="rId1"/>
@@ -27,6 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'full combined'!$A$1:$AU$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -10944,8 +10945,8 @@
   <dimension ref="A1:AV278"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="40" max="40" width="9.140625" style="6"/>
-    <col min="47" max="47" width="9.140625" style="6"/>
+    <col min="40" max="40" width="13.140625" style="6" customWidth="1"/>
+    <col min="47" max="47" width="15.28515625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:48" x14ac:dyDescent="0.25">

--- a/Data/RossSea_Phenology_estimates2025.xlsx
+++ b/Data/RossSea_Phenology_estimates2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ucliveac-my.sharepoint.com/personal/rose_foster-dyer_canterbury_ac_nz/Documents/Github/SAR_RossSea_compare/SAR_RossSea_compare/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="746" documentId="8_{C36C3FC0-118D-426B-A4A0-6E6EFE06D4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2842CF00-ADF4-418C-B4AB-77FEC13AA405}"/>
+  <xr:revisionPtr revIDLastSave="755" documentId="8_{C36C3FC0-118D-426B-A4A0-6E6EFE06D4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEB78AEC-0790-4EA2-B257-B12B132286CF}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="555" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D741B97E-D510-4026-838A-5DA85EBB5CBC}"/>
   </bookViews>
@@ -11089,7 +11089,7 @@
         <v>898</v>
       </c>
       <c r="AU1" s="6" t="s">
-        <v>1083</v>
+        <v>899</v>
       </c>
       <c r="AV1" t="s">
         <v>110</v>
@@ -20374,6 +20374,7 @@
   <dimension ref="A1:AJ63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="13" customWidth="1"/>
     <col min="27" max="27" width="9.140625" style="6"/>
     <col min="34" max="34" width="9.140625" style="6"/>
   </cols>
@@ -23023,7 +23024,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>723</v>
       </c>
@@ -27075,7 +27076,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D79535D-2933-4CEB-9607-4FF41415F045}">
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="12.7109375" customWidth="1"/>
@@ -27956,6 +27957,30 @@
         <f t="shared" si="1"/>
         <v>20682.48</v>
       </c>
+    </row>
+    <row r="22" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J22" s="6"/>
+    </row>
+    <row r="23" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J23" s="6"/>
+    </row>
+    <row r="24" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J24" s="6"/>
+    </row>
+    <row r="25" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J25" s="6"/>
+    </row>
+    <row r="26" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J26" s="6"/>
+    </row>
+    <row r="27" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J27" s="6"/>
+    </row>
+    <row r="28" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J28" s="6"/>
+    </row>
+    <row r="29" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J29" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/RossSea_Phenology_estimates2025.xlsx
+++ b/Data/RossSea_Phenology_estimates2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ucliveac-my.sharepoint.com/personal/rose_foster-dyer_canterbury_ac_nz/Documents/Github/SAR_RossSea_compare/SAR_RossSea_compare/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="755" documentId="8_{C36C3FC0-118D-426B-A4A0-6E6EFE06D4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEB78AEC-0790-4EA2-B257-B12B132286CF}"/>
+  <xr:revisionPtr revIDLastSave="756" documentId="8_{C36C3FC0-118D-426B-A4A0-6E6EFE06D4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0075C2C9-A218-4A64-9024-B5B4D006EC64}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="555" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D741B97E-D510-4026-838A-5DA85EBB5CBC}"/>
+    <workbookView xWindow="28680" yWindow="555" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{D741B97E-D510-4026-838A-5DA85EBB5CBC}"/>
   </bookViews>
   <sheets>
     <sheet name="full combined" sheetId="9" r:id="rId1"/>
@@ -20480,7 +20480,7 @@
         <v>898</v>
       </c>
       <c r="AH1" s="6" t="s">
-        <v>1083</v>
+        <v>899</v>
       </c>
       <c r="AI1" t="s">
         <v>110</v>

--- a/Data/RossSea_Phenology_estimates2025.xlsx
+++ b/Data/RossSea_Phenology_estimates2025.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="756" documentId="8_{C36C3FC0-118D-426B-A4A0-6E6EFE06D4BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0075C2C9-A218-4A64-9024-B5B4D006EC64}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="555" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{D741B97E-D510-4026-838A-5DA85EBB5CBC}"/>
+    <workbookView xWindow="28680" yWindow="555" windowWidth="29040" windowHeight="15720" xr2:uid="{D741B97E-D510-4026-838A-5DA85EBB5CBC}"/>
   </bookViews>
   <sheets>
     <sheet name="full combined" sheetId="9" r:id="rId1"/>
